--- a/Collections/EURO/Slovakia/#EURO#Slovakia#Regular#[2009-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Slovakia/#EURO#Slovakia#Regular#[2009-present]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Slovakia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F00580-FD52-4070-BFDB-EB8D38377EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784A4590-5E96-4E2A-93FB-75AD78CFE567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -388,7 +391,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="113">
   <si>
     <t>-</t>
   </si>
@@ -689,6 +692,45 @@
   </si>
   <si>
     <t>Subtype_2#Map_of_Europe</t>
+  </si>
+  <si>
+    <t>12.900</t>
+  </si>
+  <si>
+    <t>14.800</t>
+  </si>
+  <si>
+    <t>25.200</t>
+  </si>
+  <si>
+    <t>6.950</t>
+  </si>
+  <si>
+    <t>25.400</t>
+  </si>
+  <si>
+    <t>7.024.400</t>
+  </si>
+  <si>
+    <t>17.006.000</t>
+  </si>
+  <si>
+    <t>5.024.400</t>
+  </si>
+  <si>
+    <t>9.006.000</t>
+  </si>
+  <si>
+    <t>1.024.400</t>
+  </si>
+  <si>
+    <t>1.006.000</t>
+  </si>
+  <si>
+    <t>2.324.400</t>
+  </si>
+  <si>
+    <t>5.006.000</t>
   </si>
 </sst>
 </file>
@@ -997,10 +1039,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1009,7 +1051,175 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="61">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1346,9 +1556,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="22" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1617,7 +1827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1987,7 +2197,7 @@
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="23" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>0</v>
@@ -2009,13 +2219,57 @@
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="23" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G18" s="3" t="str">
         <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f t="shared" ref="G19:G20" si="4">IF(OR(AND(F19&gt;1,F19&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -2027,11 +2281,43 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F3:F13 F16">
-    <cfRule type="containsText" dxfId="39" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F13 F16">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="containsText" dxfId="59" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="containsText" dxfId="58" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2043,12 +2329,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="38" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
+  <conditionalFormatting sqref="F18">
+    <cfRule type="containsText" dxfId="57" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2060,24 +2344,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="containsText" dxfId="37" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
-    <cfRule type="containsText" dxfId="36" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="containsText" dxfId="56" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -2090,9 +2359,24 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="35" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -2444,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="str">
-        <f t="shared" ref="G15:G17" si="1">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G15:G19" si="1">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2492,11 +2776,47 @@
         <v/>
       </c>
     </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19"/>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
+      <c r="A19" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20"/>
@@ -2512,11 +2832,41 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F3:F5 F8:F13">
-    <cfRule type="containsText" dxfId="34" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="55" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F5 F8:F13">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="54" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="53" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2528,10 +2878,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="33" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F14:F15">
+    <cfRule type="containsText" dxfId="52" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F15">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2543,9 +2895,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="32" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="containsText" dxfId="51" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
       <colorScale>
@@ -2558,12 +2910,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F15">
-    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F15">
+  <conditionalFormatting sqref="F17">
+    <cfRule type="containsText" dxfId="50" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2575,9 +2925,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -2590,9 +2940,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -2613,7 +2963,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2944,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="str">
-        <f t="shared" ref="G15:G17" si="1">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G15:G19" si="1">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2989,6 +3339,50 @@
       </c>
       <c r="G17" s="3" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f t="shared" ref="G18" si="2">IF(OR(AND(F18&gt;1,F18&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f t="shared" ref="G19" si="3">IF(OR(AND(F19&gt;1,F19&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3000,12 +3394,12 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F3 F11:F13 F15 F17">
-    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="49" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F13 F3 F15 F17">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3017,9 +3411,43 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F10">
-    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="48" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14 F16">
+    <cfRule type="containsText" dxfId="47" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14 F16">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3031,12 +3459,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14 F16">
-    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16 F14">
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3056,7 +3484,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3075,7 +3503,7 @@
       <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
@@ -3085,7 +3513,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
         <v>96</v>
       </c>
@@ -3462,6 +3890,54 @@
       </c>
       <c r="G17" s="3" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f t="shared" ref="G18:G19" si="2">IF(OR(AND(F18&gt;1,F18&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3473,11 +3949,43 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F3 F13 F15 F17">
-    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="46" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13 F3 F15 F17">
+  <conditionalFormatting sqref="F3 F13 F15 F17">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:F12">
+    <cfRule type="containsText" dxfId="45" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14 F16">
+    <cfRule type="containsText" dxfId="44" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14 F16">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3489,10 +3997,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F12">
-    <cfRule type="containsText" dxfId="24" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3504,12 +4014,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14 F16">
-    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16 F14">
+  <conditionalFormatting sqref="F18">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3529,7 +4039,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3548,7 +4058,7 @@
       <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
@@ -3558,7 +4068,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
         <v>96</v>
       </c>
@@ -3886,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="str">
-        <f t="shared" ref="G15:G17" si="1">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G15:G19" si="1">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3934,6 +4444,52 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="23"/>
+      <c r="F19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3946,12 +4502,12 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="22" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3963,10 +4519,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F13">
-    <cfRule type="containsText" dxfId="21" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3978,8 +4534,38 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F17">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="41" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -4000,7 +4586,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4019,7 +4605,7 @@
       <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
@@ -4029,7 +4615,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
         <v>96</v>
       </c>
@@ -4357,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="str">
-        <f t="shared" ref="G15:G17" si="1">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G15:G19" si="1">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4405,6 +4991,52 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="23"/>
+      <c r="F19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4417,11 +5049,41 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="19" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="40" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:F13">
+    <cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F17">
+    <cfRule type="containsText" dxfId="38" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4433,9 +5095,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F13">
-    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -4448,9 +5110,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F17">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -4471,7 +5133,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4490,7 +5152,7 @@
       <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
@@ -4500,7 +5162,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
         <v>96</v>
       </c>
@@ -4829,7 +5491,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="str">
-        <f t="shared" ref="G15:G17" si="1">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G15:G19" si="1">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4881,6 +5543,54 @@
         <v/>
       </c>
       <c r="R17" s="25"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
@@ -4890,11 +5600,58 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="16" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:F13">
+    <cfRule type="containsText" dxfId="36" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16:F17 F14">
+    <cfRule type="containsText" dxfId="35" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="containsText" dxfId="34" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4906,25 +5663,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F13">
-    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F17 F14">
-    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4936,12 +5680,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
+  <conditionalFormatting sqref="F18">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4980,7 +5724,7 @@
       <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
@@ -4990,7 +5734,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
         <v>96</v>
       </c>
@@ -5319,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="str">
-        <f t="shared" ref="G15:G17" si="2">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G15:G19" si="2">IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -5367,6 +6111,54 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -5382,11 +6174,41 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F3 F5 F9:F11">
-    <cfRule type="containsText" dxfId="12" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3 F5 F9:F11">
+  <conditionalFormatting sqref="F5 F3 F9:F11">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="32" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="31" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5398,9 +6220,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="11" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="containsText" dxfId="30" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="20">
       <colorScale>
@@ -5413,9 +6235,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="10" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="containsText" dxfId="29" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
       <colorScale>
@@ -5428,9 +6250,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="9" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="containsText" dxfId="28" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
       <colorScale>
@@ -5443,9 +6265,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="containsText" dxfId="27" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
       <colorScale>
@@ -5458,25 +6280,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="containsText" dxfId="7" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F14 F16">
+    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16 F14">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5488,12 +6297,25 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14 F16">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14 F16">
+  <conditionalFormatting sqref="F15">
+    <cfRule type="containsText" dxfId="25" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5505,10 +6327,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5520,10 +6344,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F17))))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
